--- a/Side Bar Files/GWD Data/PVC wo Trench.xlsx
+++ b/Side Bar Files/GWD Data/PVC wo Trench.xlsx
@@ -15,75 +15,84 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="66">
   <si>
     <t>PVC Pipe Without Trenching</t>
   </si>
   <si>
+    <t>Providing and fixing PVC pipes includes jointing of pipes with one step PVC solvent cement &amp; testing of joints complete as per direction of Engineer in Charge. 20 mm dia 10KGF/cm2</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Rate</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Details of cost for 10 metre</t>
+  </si>
+  <si>
+    <t>MATERIALS:</t>
+  </si>
+  <si>
+    <t>MR41</t>
+  </si>
+  <si>
+    <t>PVC pipe 20 mm outer dia. 10kgf cm2</t>
+  </si>
+  <si>
+    <t>metre</t>
+  </si>
+  <si>
+    <t>Add 15% for fittings and wastage etc. on (A)</t>
+  </si>
+  <si>
+    <t>Add Water Charges @ 1%</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>Add CPOH @ 15%</t>
+  </si>
+  <si>
+    <t>Cost of 10.0 metre</t>
+  </si>
+  <si>
+    <t>Cost per metre</t>
+  </si>
+  <si>
+    <t>Fitter(grade1)</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Beldar</t>
+  </si>
+  <si>
+    <t>TOTAL  </t>
+  </si>
+  <si>
     <t>Providing and fixing PVC pipes includes jointing of pipes with one step PVC solvent cement &amp; testing of joints complete as per direction of Engineer in Charge. 25 mm dia 10KGF/cm2</t>
   </si>
   <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Unit</t>
-  </si>
-  <si>
-    <t>Quantity</t>
-  </si>
-  <si>
-    <t>Rate</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>Details of cost for 10 metre</t>
-  </si>
-  <si>
-    <t>MATERIALS:</t>
-  </si>
-  <si>
     <t>MR43</t>
   </si>
   <si>
     <t>PVC pipe 25 mm outer dia. 10kgf cm2</t>
-  </si>
-  <si>
-    <t>metre</t>
-  </si>
-  <si>
-    <t>Add 15% for fittings and wastage etc. on (A)</t>
-  </si>
-  <si>
-    <t>Add Water Charges @ 1%</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>Add CPOH @ 15%</t>
-  </si>
-  <si>
-    <t>Cost of 10.0 metre</t>
-  </si>
-  <si>
-    <t>Cost per metre</t>
-  </si>
-  <si>
-    <t>Fitter(grade1)</t>
-  </si>
-  <si>
-    <t>Day</t>
-  </si>
-  <si>
-    <t>Beldar</t>
-  </si>
-  <si>
-    <t>TOTAL  </t>
   </si>
   <si>
     <t>Providing and fixing PVC pipes includes jointing of pipes with one step PVC solvent cement &amp; testing of joints complete as per direction of Engineer in Charge. 32 mm dia 10KGF/cm2</t>
@@ -313,7 +322,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -323,6 +332,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D2E9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -445,13 +460,17 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -464,7 +483,9 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -501,7 +522,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -519,7 +540,40 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -906,8 +960,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE0CDD4-73B0-444C-A2EA-EBD78116B9A6}">
-  <dimension ref="A1:F286"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BACF584-0B85-4CFF-ACCE-0CEB0DB3B9A7}">
+  <dimension ref="A1:F308"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
     <row r="1" spans="1:6" ht="12.75">
@@ -986,11 +1040,11 @@
         <v>11.50</v>
       </c>
       <c r="E6" s="9">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="F6" s="10">
         <f>D6*E6</f>
-        <v>552</v>
+        <v>345</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="12.75">
@@ -1013,7 +1067,7 @@
       <c r="E8" s="3"/>
       <c r="F8" s="12">
         <f>F6*0.01</f>
-        <v>5.52</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="12.75">
@@ -1026,7 +1080,7 @@
       <c r="E9" s="3"/>
       <c r="F9" s="12">
         <f>SUM(F6:F8)</f>
-        <v>557.52</v>
+        <v>348.45</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="12.75">
@@ -1039,7 +1093,7 @@
       <c r="E10" s="3"/>
       <c r="F10" s="12">
         <f>F9*0.15</f>
-        <v>83.628</v>
+        <v>52.2675</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="12.75">
@@ -1052,7 +1106,7 @@
       <c r="E11" s="3"/>
       <c r="F11" s="12">
         <f>SUM(F9:F10)</f>
-        <v>641.14800000000002</v>
+        <v>400.7175</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="12.75">
@@ -1065,7 +1119,7 @@
       <c r="E12" s="3"/>
       <c r="F12" s="12">
         <f>F11</f>
-        <v>641.14800000000002</v>
+        <v>400.7175</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="12.75">
@@ -1078,7 +1132,7 @@
       <c r="E13" s="3"/>
       <c r="F13" s="13">
         <f>ROUND(F12/10,2)</f>
-        <v>64.11</v>
+        <v>40.07</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="12.75">
@@ -1092,14 +1146,14 @@
         <v>20</v>
       </c>
       <c r="D14" s="14">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="E14" s="14">
         <v>784</v>
       </c>
       <c r="F14" s="12">
         <f>D14*E14</f>
-        <v>94.08</v>
+        <v>62.72</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="12.75">
@@ -1113,14 +1167,14 @@
         <v>20</v>
       </c>
       <c r="D15" s="14">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="E15" s="14">
         <v>645</v>
       </c>
       <c r="F15" s="12">
         <f>D15*E15</f>
-        <v>161.25</v>
+        <v>103.20</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="12.75">
@@ -1133,7 +1187,7 @@
       <c r="E16" s="3"/>
       <c r="F16" s="12">
         <f>SUM(F14:F15)</f>
-        <v>255.33</v>
+        <v>165.92</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="12.75">
@@ -1146,7 +1200,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="12">
         <f>F16*0.01</f>
-        <v>2.5533000000000001</v>
+        <v>1.6592</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="12.75">
@@ -1159,7 +1213,7 @@
       <c r="E18" s="3"/>
       <c r="F18" s="12">
         <f>SUM(F16:F17)</f>
-        <v>257.88330000000002</v>
+        <v>167.57919999999999</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="12.75">
@@ -1172,7 +1226,7 @@
       <c r="E19" s="3"/>
       <c r="F19" s="12">
         <f>F18*0.15</f>
-        <v>38.682495000000003</v>
+        <v>25.136880000000001</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="12.75">
@@ -1185,7 +1239,7 @@
       <c r="E20" s="3"/>
       <c r="F20" s="12">
         <f>SUM(F18:F19)</f>
-        <v>296.56579499999998</v>
+        <v>192.71608000000001</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="12.75">
@@ -1198,7 +1252,7 @@
       <c r="E21" s="3"/>
       <c r="F21" s="12">
         <f>F20</f>
-        <v>296.56579499999998</v>
+        <v>192.71608000000001</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="12.75">
@@ -1211,13 +1265,13 @@
       <c r="E22" s="3"/>
       <c r="F22" s="13">
         <f>ROUND(F21/10,2)</f>
-        <v>29.66</v>
+        <v>19.27</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="12.75">
       <c r="A23" s="15" t="str">
         <f>CONCATENATE("Say ₹ ",F13," + ",F22," x Cost Index")</f>
-        <v>Say ₹ 64.11 + 29.66 x Cost Index</v>
+        <v>Say ₹ 40.07 + 19.27 x Cost Index</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1291,11 +1345,11 @@
         <v>11.50</v>
       </c>
       <c r="E28" s="20">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="F28" s="21">
         <f>D28*E28</f>
-        <v>747.50</v>
+        <v>552</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="12.75">
@@ -1318,7 +1372,7 @@
       <c r="E30" s="3"/>
       <c r="F30" s="23">
         <f>F28*0.01</f>
-        <v>7.475</v>
+        <v>5.52</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="12.75">
@@ -1331,7 +1385,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="23">
         <f>SUM(F28:F30)</f>
-        <v>754.975</v>
+        <v>557.52</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="12.75">
@@ -1344,7 +1398,7 @@
       <c r="E32" s="3"/>
       <c r="F32" s="23">
         <f>F31*0.15</f>
-        <v>113.24625</v>
+        <v>83.628</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="12.75">
@@ -1357,7 +1411,7 @@
       <c r="E33" s="3"/>
       <c r="F33" s="23">
         <f>SUM(F31:F32)</f>
-        <v>868.22125000000005</v>
+        <v>641.14800000000002</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="12.75">
@@ -1370,7 +1424,7 @@
       <c r="E34" s="3"/>
       <c r="F34" s="23">
         <f>F33</f>
-        <v>868.22125000000005</v>
+        <v>641.14800000000002</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="12.75">
@@ -1383,7 +1437,7 @@
       <c r="E35" s="3"/>
       <c r="F35" s="24">
         <f>ROUND(F34/10,2)</f>
-        <v>86.82</v>
+        <v>64.11</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="12.75">
@@ -1522,7 +1576,7 @@
     <row r="45" spans="1:6" ht="12.75">
       <c r="A45" s="26" t="str">
         <f>CONCATENATE("Say ₹ ",F35," + ",F44," x Cost Index")</f>
-        <v>Say ₹ 86.82 + 29.66 x Cost Index</v>
+        <v>Say ₹ 64.11 + 29.66 x Cost Index</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -1531,10 +1585,10 @@
       <c r="F45" s="3"/>
     </row>
     <row r="46" spans="1:6" ht="12.75">
-      <c r="A46" s="4">
+      <c r="A46" s="27">
         <v>0</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="28" t="s">
         <v>26</v>
       </c>
       <c r="C46" s="2"/>
@@ -1543,38 +1597,38 @@
       <c r="F46" s="3"/>
     </row>
     <row r="47" spans="1:6" ht="12.75">
-      <c r="A47" s="4" t="s">
+      <c r="A47" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C47" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D47" s="4" t="s">
+      <c r="D47" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="27" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="12.75">
-      <c r="A48" s="6"/>
-      <c r="B48" s="7" t="s">
+      <c r="A48" s="29"/>
+      <c r="B48" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C48" s="6"/>
-      <c r="D48" s="6"/>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
+      <c r="C48" s="29"/>
+      <c r="D48" s="29"/>
+      <c r="E48" s="29"/>
+      <c r="F48" s="29"/>
     </row>
     <row r="49" spans="1:6" ht="12.75">
       <c r="A49" s="8"/>
-      <c r="B49" s="7" t="s">
+      <c r="B49" s="30" t="s">
         <v>9</v>
       </c>
       <c r="C49" s="8"/>
@@ -1583,29 +1637,29 @@
       <c r="F49" s="8"/>
     </row>
     <row r="50" spans="1:6" ht="12.75">
-      <c r="A50" s="9" t="s">
+      <c r="A50" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="B50" s="7" t="s">
+      <c r="B50" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C50" s="9" t="s">
+      <c r="C50" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="D50" s="9">
+      <c r="D50" s="31">
         <v>11.50</v>
       </c>
-      <c r="E50" s="9">
-        <v>52</v>
-      </c>
-      <c r="F50" s="10">
+      <c r="E50" s="31">
+        <v>65</v>
+      </c>
+      <c r="F50" s="32">
         <f>D50*E50</f>
-        <v>598</v>
+        <v>747.50</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="12.75">
       <c r="A51" s="8"/>
-      <c r="B51" s="7" t="s">
+      <c r="B51" s="30" t="s">
         <v>13</v>
       </c>
       <c r="C51" s="8"/>
@@ -1614,220 +1668,220 @@
       <c r="F51" s="8"/>
     </row>
     <row r="52" spans="1:6" ht="12.75">
-      <c r="A52" s="7"/>
-      <c r="B52" s="11" t="s">
+      <c r="A52" s="30"/>
+      <c r="B52" s="33" t="s">
         <v>14</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
       <c r="E52" s="3"/>
-      <c r="F52" s="12">
+      <c r="F52" s="34">
         <f>F50*0.01</f>
-        <v>5.98</v>
+        <v>7.475</v>
       </c>
     </row>
     <row r="53" spans="1:6" ht="12.75">
-      <c r="A53" s="7"/>
-      <c r="B53" s="11" t="s">
+      <c r="A53" s="30"/>
+      <c r="B53" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
       <c r="E53" s="3"/>
-      <c r="F53" s="12">
+      <c r="F53" s="34">
         <f>SUM(F50:F52)</f>
-        <v>603.98</v>
+        <v>754.975</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="12.75">
-      <c r="A54" s="7"/>
-      <c r="B54" s="11" t="s">
+      <c r="A54" s="30"/>
+      <c r="B54" s="33" t="s">
         <v>16</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
       <c r="E54" s="3"/>
-      <c r="F54" s="12">
+      <c r="F54" s="34">
         <f>F53*0.15</f>
-        <v>90.596999999999994</v>
+        <v>113.24625</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="12.75">
-      <c r="A55" s="7"/>
-      <c r="B55" s="11" t="s">
+      <c r="A55" s="30"/>
+      <c r="B55" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
       <c r="E55" s="3"/>
-      <c r="F55" s="12">
+      <c r="F55" s="34">
         <f>SUM(F53:F54)</f>
-        <v>694.577</v>
+        <v>868.22125000000005</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="12.75">
-      <c r="A56" s="7"/>
-      <c r="B56" s="11" t="s">
+      <c r="A56" s="30"/>
+      <c r="B56" s="33" t="s">
         <v>17</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
       <c r="E56" s="3"/>
-      <c r="F56" s="12">
+      <c r="F56" s="34">
         <f>F55</f>
-        <v>694.577</v>
+        <v>868.22125000000005</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="12.75">
-      <c r="A57" s="7"/>
-      <c r="B57" s="11" t="s">
+      <c r="A57" s="30"/>
+      <c r="B57" s="33" t="s">
         <v>18</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
       <c r="E57" s="3"/>
-      <c r="F57" s="13">
+      <c r="F57" s="35">
         <f>ROUND(F56/10,2)</f>
-        <v>69.46</v>
+        <v>86.82</v>
       </c>
     </row>
     <row r="58" spans="1:6" ht="12.75">
-      <c r="A58" s="14">
+      <c r="A58" s="36">
         <v>116</v>
       </c>
-      <c r="B58" s="7" t="s">
+      <c r="B58" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C58" s="14" t="s">
+      <c r="C58" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="D58" s="14">
+      <c r="D58" s="36">
         <v>0.12</v>
       </c>
-      <c r="E58" s="14">
+      <c r="E58" s="36">
         <v>784</v>
       </c>
-      <c r="F58" s="12">
+      <c r="F58" s="34">
         <f>D58*E58</f>
         <v>94.08</v>
       </c>
     </row>
     <row r="59" spans="1:6" ht="12.75">
-      <c r="A59" s="14">
+      <c r="A59" s="36">
         <v>114</v>
       </c>
-      <c r="B59" s="7" t="s">
+      <c r="B59" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C59" s="14" t="s">
+      <c r="C59" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="D59" s="14">
+      <c r="D59" s="36">
         <v>0.25</v>
       </c>
-      <c r="E59" s="14">
+      <c r="E59" s="36">
         <v>645</v>
       </c>
-      <c r="F59" s="12">
+      <c r="F59" s="34">
         <f>D59*E59</f>
         <v>161.25</v>
       </c>
     </row>
     <row r="60" spans="1:6" ht="12.75">
-      <c r="A60" s="7"/>
-      <c r="B60" s="11" t="s">
+      <c r="A60" s="30"/>
+      <c r="B60" s="33" t="s">
         <v>22</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="3"/>
-      <c r="F60" s="12">
+      <c r="F60" s="34">
         <f>SUM(F58:F59)</f>
         <v>255.33</v>
       </c>
     </row>
     <row r="61" spans="1:6" ht="12.75">
-      <c r="A61" s="7"/>
-      <c r="B61" s="11" t="s">
+      <c r="A61" s="30"/>
+      <c r="B61" s="33" t="s">
         <v>14</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
       <c r="E61" s="3"/>
-      <c r="F61" s="12">
+      <c r="F61" s="34">
         <f>F60*0.01</f>
         <v>2.5533000000000001</v>
       </c>
     </row>
     <row r="62" spans="1:6" ht="12.75">
-      <c r="A62" s="7"/>
-      <c r="B62" s="11" t="s">
+      <c r="A62" s="30"/>
+      <c r="B62" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
       <c r="E62" s="3"/>
-      <c r="F62" s="12">
+      <c r="F62" s="34">
         <f>SUM(F60:F61)</f>
         <v>257.88330000000002</v>
       </c>
     </row>
     <row r="63" spans="1:6" ht="12.75">
-      <c r="A63" s="7"/>
-      <c r="B63" s="11" t="s">
+      <c r="A63" s="30"/>
+      <c r="B63" s="33" t="s">
         <v>16</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
       <c r="E63" s="3"/>
-      <c r="F63" s="12">
+      <c r="F63" s="34">
         <f>F62*0.15</f>
         <v>38.682495000000003</v>
       </c>
     </row>
     <row r="64" spans="1:6" ht="12.75">
-      <c r="A64" s="7"/>
-      <c r="B64" s="11" t="s">
+      <c r="A64" s="30"/>
+      <c r="B64" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
       <c r="E64" s="3"/>
-      <c r="F64" s="12">
+      <c r="F64" s="34">
         <f>SUM(F62:F63)</f>
         <v>296.56579499999998</v>
       </c>
     </row>
     <row r="65" spans="1:6" ht="12.75">
-      <c r="A65" s="7"/>
-      <c r="B65" s="11" t="s">
+      <c r="A65" s="30"/>
+      <c r="B65" s="33" t="s">
         <v>17</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
       <c r="E65" s="3"/>
-      <c r="F65" s="12">
+      <c r="F65" s="34">
         <f>F64</f>
         <v>296.56579499999998</v>
       </c>
     </row>
     <row r="66" spans="1:6" ht="12.75">
-      <c r="A66" s="7"/>
-      <c r="B66" s="11" t="s">
+      <c r="A66" s="30"/>
+      <c r="B66" s="33" t="s">
         <v>18</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
       <c r="E66" s="3"/>
-      <c r="F66" s="13">
+      <c r="F66" s="35">
         <f>ROUND(F65/10,2)</f>
         <v>29.66</v>
       </c>
     </row>
     <row r="67" spans="1:6" ht="12.75">
-      <c r="A67" s="26" t="str">
+      <c r="A67" s="37" t="str">
         <f>CONCATENATE("Say ₹ ",F57," + ",F66," x Cost Index")</f>
-        <v>Say ₹ 69.46 + 29.66 x Cost Index</v>
+        <v>Say ₹ 86.82 + 29.66 x Cost Index</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
@@ -1901,11 +1955,11 @@
         <v>11.50</v>
       </c>
       <c r="E72" s="20">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F72" s="21">
         <f>D72*E72</f>
-        <v>609.50</v>
+        <v>598</v>
       </c>
     </row>
     <row r="73" spans="1:6" ht="12.75">
@@ -1928,7 +1982,7 @@
       <c r="E74" s="3"/>
       <c r="F74" s="23">
         <f>F72*0.01</f>
-        <v>6.095</v>
+        <v>5.98</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="12.75">
@@ -1941,7 +1995,7 @@
       <c r="E75" s="3"/>
       <c r="F75" s="23">
         <f>SUM(F72:F74)</f>
-        <v>615.595</v>
+        <v>603.98</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="12.75">
@@ -1954,7 +2008,7 @@
       <c r="E76" s="3"/>
       <c r="F76" s="23">
         <f>F75*0.15</f>
-        <v>92.339250000000007</v>
+        <v>90.596999999999994</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="12.75">
@@ -1967,7 +2021,7 @@
       <c r="E77" s="3"/>
       <c r="F77" s="23">
         <f>SUM(F75:F76)</f>
-        <v>707.93425000000002</v>
+        <v>694.577</v>
       </c>
     </row>
     <row r="78" spans="1:6" ht="12.75">
@@ -1980,7 +2034,7 @@
       <c r="E78" s="3"/>
       <c r="F78" s="23">
         <f>F77</f>
-        <v>707.93425000000002</v>
+        <v>694.577</v>
       </c>
     </row>
     <row r="79" spans="1:6" ht="12.75">
@@ -1993,7 +2047,7 @@
       <c r="E79" s="3"/>
       <c r="F79" s="24">
         <f>ROUND(F78/10,2)</f>
-        <v>70.79</v>
+        <v>69.46</v>
       </c>
     </row>
     <row r="80" spans="1:6" ht="12.75">
@@ -2130,9 +2184,9 @@
       </c>
     </row>
     <row r="89" spans="1:6" ht="12.75">
-      <c r="A89" s="26" t="str">
+      <c r="A89" s="37" t="str">
         <f>CONCATENATE("Say ₹ ",F79," + ",F88," x Cost Index")</f>
-        <v>Say ₹ 70.79 + 29.66 x Cost Index</v>
+        <v>Say ₹ 69.46 + 29.66 x Cost Index</v>
       </c>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -2141,10 +2195,10 @@
       <c r="F89" s="3"/>
     </row>
     <row r="90" spans="1:6" ht="12.75">
-      <c r="A90" s="4">
+      <c r="A90" s="27">
         <v>0</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="B90" s="28" t="s">
         <v>32</v>
       </c>
       <c r="C90" s="2"/>
@@ -2153,38 +2207,38 @@
       <c r="F90" s="3"/>
     </row>
     <row r="91" spans="1:6" ht="12.75">
-      <c r="A91" s="4" t="s">
+      <c r="A91" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C91" s="4" t="s">
+      <c r="C91" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D91" s="4" t="s">
+      <c r="D91" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E91" s="4" t="s">
+      <c r="E91" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="F91" s="4" t="s">
+      <c r="F91" s="27" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:6" ht="12.75">
-      <c r="A92" s="6"/>
-      <c r="B92" s="7" t="s">
+      <c r="A92" s="29"/>
+      <c r="B92" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C92" s="6"/>
-      <c r="D92" s="6"/>
-      <c r="E92" s="6"/>
-      <c r="F92" s="6"/>
+      <c r="C92" s="29"/>
+      <c r="D92" s="29"/>
+      <c r="E92" s="29"/>
+      <c r="F92" s="29"/>
     </row>
     <row r="93" spans="1:6" ht="12.75">
       <c r="A93" s="8"/>
-      <c r="B93" s="7" t="s">
+      <c r="B93" s="30" t="s">
         <v>9</v>
       </c>
       <c r="C93" s="8"/>
@@ -2193,29 +2247,29 @@
       <c r="F93" s="8"/>
     </row>
     <row r="94" spans="1:6" ht="12.75">
-      <c r="A94" s="9" t="s">
+      <c r="A94" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="B94" s="7" t="s">
+      <c r="B94" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="C94" s="9" t="s">
+      <c r="C94" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="D94" s="9">
+      <c r="D94" s="31">
         <v>11.50</v>
       </c>
-      <c r="E94" s="9">
-        <v>84</v>
-      </c>
-      <c r="F94" s="10">
+      <c r="E94" s="31">
+        <v>53</v>
+      </c>
+      <c r="F94" s="32">
         <f>D94*E94</f>
-        <v>966</v>
+        <v>609.50</v>
       </c>
     </row>
     <row r="95" spans="1:6" ht="12.75">
       <c r="A95" s="8"/>
-      <c r="B95" s="7" t="s">
+      <c r="B95" s="30" t="s">
         <v>13</v>
       </c>
       <c r="C95" s="8"/>
@@ -2224,220 +2278,220 @@
       <c r="F95" s="8"/>
     </row>
     <row r="96" spans="1:6" ht="12.75">
-      <c r="A96" s="7"/>
-      <c r="B96" s="11" t="s">
+      <c r="A96" s="30"/>
+      <c r="B96" s="33" t="s">
         <v>14</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
       <c r="E96" s="3"/>
-      <c r="F96" s="12">
+      <c r="F96" s="34">
         <f>F94*0.01</f>
-        <v>9.66</v>
+        <v>6.095</v>
       </c>
     </row>
     <row r="97" spans="1:6" ht="12.75">
-      <c r="A97" s="7"/>
-      <c r="B97" s="11" t="s">
+      <c r="A97" s="30"/>
+      <c r="B97" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
       <c r="E97" s="3"/>
-      <c r="F97" s="12">
+      <c r="F97" s="34">
         <f>SUM(F94:F96)</f>
-        <v>975.66</v>
+        <v>615.595</v>
       </c>
     </row>
     <row r="98" spans="1:6" ht="12.75">
-      <c r="A98" s="7"/>
-      <c r="B98" s="11" t="s">
+      <c r="A98" s="30"/>
+      <c r="B98" s="33" t="s">
         <v>16</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
       <c r="E98" s="3"/>
-      <c r="F98" s="12">
+      <c r="F98" s="34">
         <f>F97*0.15</f>
-        <v>146.34899999999999</v>
+        <v>92.339250000000007</v>
       </c>
     </row>
     <row r="99" spans="1:6" ht="12.75">
-      <c r="A99" s="7"/>
-      <c r="B99" s="11" t="s">
+      <c r="A99" s="30"/>
+      <c r="B99" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
       <c r="E99" s="3"/>
-      <c r="F99" s="12">
+      <c r="F99" s="34">
         <f>SUM(F97:F98)</f>
-        <v>1122.009</v>
+        <v>707.93425000000002</v>
       </c>
     </row>
     <row r="100" spans="1:6" ht="12.75">
-      <c r="A100" s="7"/>
-      <c r="B100" s="11" t="s">
+      <c r="A100" s="30"/>
+      <c r="B100" s="33" t="s">
         <v>17</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
       <c r="E100" s="3"/>
-      <c r="F100" s="12">
+      <c r="F100" s="34">
         <f>F99</f>
-        <v>1122.009</v>
+        <v>707.93425000000002</v>
       </c>
     </row>
     <row r="101" spans="1:6" ht="12.75">
-      <c r="A101" s="7"/>
-      <c r="B101" s="11" t="s">
+      <c r="A101" s="30"/>
+      <c r="B101" s="33" t="s">
         <v>18</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
       <c r="E101" s="3"/>
-      <c r="F101" s="13">
+      <c r="F101" s="35">
         <f>ROUND(F100/10,2)</f>
-        <v>112.20</v>
+        <v>70.79</v>
       </c>
     </row>
     <row r="102" spans="1:6" ht="12.75">
-      <c r="A102" s="14">
+      <c r="A102" s="36">
         <v>116</v>
       </c>
-      <c r="B102" s="7" t="s">
+      <c r="B102" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C102" s="14" t="s">
+      <c r="C102" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="D102" s="14">
+      <c r="D102" s="36">
         <v>0.12</v>
       </c>
-      <c r="E102" s="14">
+      <c r="E102" s="36">
         <v>784</v>
       </c>
-      <c r="F102" s="12">
+      <c r="F102" s="34">
         <f>D102*E102</f>
         <v>94.08</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="12.75">
-      <c r="A103" s="14">
+      <c r="A103" s="36">
         <v>114</v>
       </c>
-      <c r="B103" s="7" t="s">
+      <c r="B103" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C103" s="14" t="s">
+      <c r="C103" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="D103" s="14">
+      <c r="D103" s="36">
         <v>0.25</v>
       </c>
-      <c r="E103" s="14">
+      <c r="E103" s="36">
         <v>645</v>
       </c>
-      <c r="F103" s="12">
+      <c r="F103" s="34">
         <f>D103*E103</f>
         <v>161.25</v>
       </c>
     </row>
     <row r="104" spans="1:6" ht="12.75">
-      <c r="A104" s="7"/>
-      <c r="B104" s="11" t="s">
+      <c r="A104" s="30"/>
+      <c r="B104" s="33" t="s">
         <v>22</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
       <c r="E104" s="3"/>
-      <c r="F104" s="12">
+      <c r="F104" s="34">
         <f>SUM(F102:F103)</f>
         <v>255.33</v>
       </c>
     </row>
     <row r="105" spans="1:6" ht="12.75">
-      <c r="A105" s="7"/>
-      <c r="B105" s="11" t="s">
+      <c r="A105" s="30"/>
+      <c r="B105" s="33" t="s">
         <v>14</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" s="2"/>
       <c r="E105" s="3"/>
-      <c r="F105" s="12">
+      <c r="F105" s="34">
         <f>F104*0.01</f>
         <v>2.5533000000000001</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="12.75">
-      <c r="A106" s="7"/>
-      <c r="B106" s="11" t="s">
+      <c r="A106" s="30"/>
+      <c r="B106" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
       <c r="E106" s="3"/>
-      <c r="F106" s="12">
+      <c r="F106" s="34">
         <f>SUM(F104:F105)</f>
         <v>257.88330000000002</v>
       </c>
     </row>
     <row r="107" spans="1:6" ht="12.75">
-      <c r="A107" s="7"/>
-      <c r="B107" s="11" t="s">
+      <c r="A107" s="30"/>
+      <c r="B107" s="33" t="s">
         <v>16</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" s="2"/>
       <c r="E107" s="3"/>
-      <c r="F107" s="12">
+      <c r="F107" s="34">
         <f>F106*0.15</f>
         <v>38.682495000000003</v>
       </c>
     </row>
     <row r="108" spans="1:6" ht="12.75">
-      <c r="A108" s="7"/>
-      <c r="B108" s="11" t="s">
+      <c r="A108" s="30"/>
+      <c r="B108" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
       <c r="E108" s="3"/>
-      <c r="F108" s="12">
+      <c r="F108" s="34">
         <f>SUM(F106:F107)</f>
         <v>296.56579499999998</v>
       </c>
     </row>
     <row r="109" spans="1:6" ht="12.75">
-      <c r="A109" s="7"/>
-      <c r="B109" s="11" t="s">
+      <c r="A109" s="30"/>
+      <c r="B109" s="33" t="s">
         <v>17</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
       <c r="E109" s="3"/>
-      <c r="F109" s="12">
+      <c r="F109" s="34">
         <f>F108</f>
         <v>296.56579499999998</v>
       </c>
     </row>
     <row r="110" spans="1:6" ht="12.75">
-      <c r="A110" s="7"/>
-      <c r="B110" s="11" t="s">
+      <c r="A110" s="30"/>
+      <c r="B110" s="33" t="s">
         <v>18</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" s="2"/>
       <c r="E110" s="3"/>
-      <c r="F110" s="13">
+      <c r="F110" s="35">
         <f>ROUND(F109/10,2)</f>
         <v>29.66</v>
       </c>
     </row>
     <row r="111" spans="1:6" ht="12.75">
-      <c r="A111" s="26" t="str">
+      <c r="A111" s="37" t="str">
         <f>CONCATENATE("Say ₹ ",F101," + ",F110," x Cost Index")</f>
-        <v>Say ₹ 112.2 + 29.66 x Cost Index</v>
+        <v>Say ₹ 70.79 + 29.66 x Cost Index</v>
       </c>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -2511,11 +2565,11 @@
         <v>11.50</v>
       </c>
       <c r="E116" s="20">
-        <v>60</v>
-      </c>
-      <c r="F116" s="27">
+        <v>84</v>
+      </c>
+      <c r="F116" s="21">
         <f>D116*E116</f>
-        <v>690</v>
+        <v>966</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="12.75">
@@ -2538,7 +2592,7 @@
       <c r="E118" s="3"/>
       <c r="F118" s="23">
         <f>F116*0.01</f>
-        <v>6.90</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="119" spans="1:6" ht="12.75">
@@ -2551,7 +2605,7 @@
       <c r="E119" s="3"/>
       <c r="F119" s="23">
         <f>SUM(F116:F118)</f>
-        <v>696.90</v>
+        <v>975.66</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="12.75">
@@ -2564,7 +2618,7 @@
       <c r="E120" s="3"/>
       <c r="F120" s="23">
         <f>F119*0.15</f>
-        <v>104.535</v>
+        <v>146.34899999999999</v>
       </c>
     </row>
     <row r="121" spans="1:6" ht="12.75">
@@ -2577,7 +2631,7 @@
       <c r="E121" s="3"/>
       <c r="F121" s="23">
         <f>SUM(F119:F120)</f>
-        <v>801.435</v>
+        <v>1122.009</v>
       </c>
     </row>
     <row r="122" spans="1:6" ht="12.75">
@@ -2590,7 +2644,7 @@
       <c r="E122" s="3"/>
       <c r="F122" s="23">
         <f>F121</f>
-        <v>801.435</v>
+        <v>1122.009</v>
       </c>
     </row>
     <row r="123" spans="1:6" ht="12.75">
@@ -2603,7 +2657,7 @@
       <c r="E123" s="3"/>
       <c r="F123" s="24">
         <f>ROUND(F122/10,2)</f>
-        <v>80.14</v>
+        <v>112.20</v>
       </c>
     </row>
     <row r="124" spans="1:6" ht="12.75">
@@ -2740,9 +2794,9 @@
       </c>
     </row>
     <row r="133" spans="1:6" ht="12.75">
-      <c r="A133" s="26" t="str">
+      <c r="A133" s="37" t="str">
         <f>CONCATENATE("Say ₹ ",F123," + ",F132," x Cost Index")</f>
-        <v>Say ₹ 80.14 + 29.66 x Cost Index</v>
+        <v>Say ₹ 112.2 + 29.66 x Cost Index</v>
       </c>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -2751,10 +2805,10 @@
       <c r="F133" s="3"/>
     </row>
     <row r="134" spans="1:6" ht="12.75">
-      <c r="A134" s="4">
+      <c r="A134" s="27">
         <v>0</v>
       </c>
-      <c r="B134" s="5" t="s">
+      <c r="B134" s="28" t="s">
         <v>38</v>
       </c>
       <c r="C134" s="2"/>
@@ -2763,38 +2817,38 @@
       <c r="F134" s="3"/>
     </row>
     <row r="135" spans="1:6" ht="12.75">
-      <c r="A135" s="4" t="s">
+      <c r="A135" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B135" s="4" t="s">
+      <c r="B135" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C135" s="4" t="s">
+      <c r="C135" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D135" s="4" t="s">
+      <c r="D135" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E135" s="4" t="s">
+      <c r="E135" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="F135" s="4" t="s">
+      <c r="F135" s="27" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="136" spans="1:6" ht="12.75">
-      <c r="A136" s="6"/>
-      <c r="B136" s="7" t="s">
+      <c r="A136" s="29"/>
+      <c r="B136" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C136" s="6"/>
-      <c r="D136" s="6"/>
-      <c r="E136" s="6"/>
-      <c r="F136" s="6"/>
+      <c r="C136" s="29"/>
+      <c r="D136" s="29"/>
+      <c r="E136" s="29"/>
+      <c r="F136" s="29"/>
     </row>
     <row r="137" spans="1:6" ht="12.75">
       <c r="A137" s="8"/>
-      <c r="B137" s="7" t="s">
+      <c r="B137" s="30" t="s">
         <v>9</v>
       </c>
       <c r="C137" s="8"/>
@@ -2803,29 +2857,29 @@
       <c r="F137" s="8"/>
     </row>
     <row r="138" spans="1:6" ht="12.75">
-      <c r="A138" s="9" t="s">
+      <c r="A138" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="B138" s="7" t="s">
+      <c r="B138" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="C138" s="9" t="s">
+      <c r="C138" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="D138" s="9">
+      <c r="D138" s="31">
         <v>11.50</v>
       </c>
-      <c r="E138" s="9">
-        <v>90</v>
-      </c>
-      <c r="F138" s="10">
+      <c r="E138" s="31">
+        <v>60</v>
+      </c>
+      <c r="F138" s="38">
         <f>D138*E138</f>
-        <v>1035</v>
+        <v>690</v>
       </c>
     </row>
     <row r="139" spans="1:6" ht="12.75">
       <c r="A139" s="8"/>
-      <c r="B139" s="7" t="s">
+      <c r="B139" s="30" t="s">
         <v>13</v>
       </c>
       <c r="C139" s="8"/>
@@ -2834,220 +2888,220 @@
       <c r="F139" s="8"/>
     </row>
     <row r="140" spans="1:6" ht="12.75">
-      <c r="A140" s="7"/>
-      <c r="B140" s="11" t="s">
+      <c r="A140" s="30"/>
+      <c r="B140" s="33" t="s">
         <v>14</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" s="2"/>
       <c r="E140" s="3"/>
-      <c r="F140" s="12">
+      <c r="F140" s="34">
         <f>F138*0.01</f>
-        <v>10.35</v>
+        <v>6.90</v>
       </c>
     </row>
     <row r="141" spans="1:6" ht="12.75">
-      <c r="A141" s="7"/>
-      <c r="B141" s="11" t="s">
+      <c r="A141" s="30"/>
+      <c r="B141" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" s="2"/>
       <c r="E141" s="3"/>
-      <c r="F141" s="12">
+      <c r="F141" s="34">
         <f>SUM(F138:F140)</f>
-        <v>1045.35</v>
+        <v>696.90</v>
       </c>
     </row>
     <row r="142" spans="1:6" ht="12.75">
-      <c r="A142" s="7"/>
-      <c r="B142" s="11" t="s">
+      <c r="A142" s="30"/>
+      <c r="B142" s="33" t="s">
         <v>16</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" s="2"/>
       <c r="E142" s="3"/>
-      <c r="F142" s="12">
+      <c r="F142" s="34">
         <f>F141*0.15</f>
-        <v>156.8025</v>
+        <v>104.535</v>
       </c>
     </row>
     <row r="143" spans="1:6" ht="12.75">
-      <c r="A143" s="7"/>
-      <c r="B143" s="11" t="s">
+      <c r="A143" s="30"/>
+      <c r="B143" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" s="2"/>
       <c r="E143" s="3"/>
-      <c r="F143" s="12">
+      <c r="F143" s="34">
         <f>SUM(F141:F142)</f>
-        <v>1202.1525</v>
+        <v>801.435</v>
       </c>
     </row>
     <row r="144" spans="1:6" ht="12.75">
-      <c r="A144" s="7"/>
-      <c r="B144" s="11" t="s">
+      <c r="A144" s="30"/>
+      <c r="B144" s="33" t="s">
         <v>17</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" s="2"/>
       <c r="E144" s="3"/>
-      <c r="F144" s="12">
+      <c r="F144" s="34">
         <f>F143</f>
-        <v>1202.1525</v>
+        <v>801.435</v>
       </c>
     </row>
     <row r="145" spans="1:6" ht="12.75">
-      <c r="A145" s="7"/>
-      <c r="B145" s="11" t="s">
+      <c r="A145" s="30"/>
+      <c r="B145" s="33" t="s">
         <v>18</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" s="2"/>
       <c r="E145" s="3"/>
-      <c r="F145" s="13">
+      <c r="F145" s="35">
         <f>ROUND(F144/10,2)</f>
-        <v>120.22</v>
+        <v>80.14</v>
       </c>
     </row>
     <row r="146" spans="1:6" ht="12.75">
-      <c r="A146" s="14">
+      <c r="A146" s="36">
         <v>116</v>
       </c>
-      <c r="B146" s="7" t="s">
+      <c r="B146" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C146" s="14" t="s">
+      <c r="C146" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="D146" s="14">
+      <c r="D146" s="36">
         <v>0.12</v>
       </c>
-      <c r="E146" s="14">
+      <c r="E146" s="36">
         <v>784</v>
       </c>
-      <c r="F146" s="12">
+      <c r="F146" s="34">
         <f>D146*E146</f>
         <v>94.08</v>
       </c>
     </row>
     <row r="147" spans="1:6" ht="12.75">
-      <c r="A147" s="14">
+      <c r="A147" s="36">
         <v>114</v>
       </c>
-      <c r="B147" s="7" t="s">
+      <c r="B147" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C147" s="14" t="s">
+      <c r="C147" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="D147" s="14">
+      <c r="D147" s="36">
         <v>0.25</v>
       </c>
-      <c r="E147" s="14">
+      <c r="E147" s="36">
         <v>645</v>
       </c>
-      <c r="F147" s="12">
+      <c r="F147" s="34">
         <f>D147*E147</f>
         <v>161.25</v>
       </c>
     </row>
     <row r="148" spans="1:6" ht="12.75">
-      <c r="A148" s="7"/>
-      <c r="B148" s="11" t="s">
+      <c r="A148" s="30"/>
+      <c r="B148" s="33" t="s">
         <v>22</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" s="2"/>
       <c r="E148" s="3"/>
-      <c r="F148" s="12">
+      <c r="F148" s="34">
         <f>SUM(F146:F147)</f>
         <v>255.33</v>
       </c>
     </row>
     <row r="149" spans="1:6" ht="12.75">
-      <c r="A149" s="7"/>
-      <c r="B149" s="11" t="s">
+      <c r="A149" s="30"/>
+      <c r="B149" s="33" t="s">
         <v>14</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" s="2"/>
       <c r="E149" s="3"/>
-      <c r="F149" s="12">
+      <c r="F149" s="34">
         <f>F148*0.01</f>
         <v>2.5533000000000001</v>
       </c>
     </row>
     <row r="150" spans="1:6" ht="12.75">
-      <c r="A150" s="7"/>
-      <c r="B150" s="11" t="s">
+      <c r="A150" s="30"/>
+      <c r="B150" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" s="2"/>
       <c r="E150" s="3"/>
-      <c r="F150" s="12">
+      <c r="F150" s="34">
         <f>SUM(F148:F149)</f>
         <v>257.88330000000002</v>
       </c>
     </row>
     <row r="151" spans="1:6" ht="12.75">
-      <c r="A151" s="7"/>
-      <c r="B151" s="11" t="s">
+      <c r="A151" s="30"/>
+      <c r="B151" s="33" t="s">
         <v>16</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" s="2"/>
       <c r="E151" s="3"/>
-      <c r="F151" s="12">
+      <c r="F151" s="34">
         <f>F150*0.15</f>
         <v>38.682495000000003</v>
       </c>
     </row>
     <row r="152" spans="1:6" ht="12.75">
-      <c r="A152" s="7"/>
-      <c r="B152" s="11" t="s">
+      <c r="A152" s="30"/>
+      <c r="B152" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" s="2"/>
       <c r="E152" s="3"/>
-      <c r="F152" s="12">
+      <c r="F152" s="34">
         <f>SUM(F150:F151)</f>
         <v>296.56579499999998</v>
       </c>
     </row>
     <row r="153" spans="1:6" ht="12.75">
-      <c r="A153" s="7"/>
-      <c r="B153" s="11" t="s">
+      <c r="A153" s="30"/>
+      <c r="B153" s="33" t="s">
         <v>17</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" s="2"/>
       <c r="E153" s="3"/>
-      <c r="F153" s="12">
+      <c r="F153" s="34">
         <f>F152</f>
         <v>296.56579499999998</v>
       </c>
     </row>
     <row r="154" spans="1:6" ht="12.75">
-      <c r="A154" s="7"/>
-      <c r="B154" s="11" t="s">
+      <c r="A154" s="30"/>
+      <c r="B154" s="33" t="s">
         <v>18</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" s="2"/>
       <c r="E154" s="3"/>
-      <c r="F154" s="13">
+      <c r="F154" s="35">
         <f>ROUND(F153/10,2)</f>
         <v>29.66</v>
       </c>
     </row>
     <row r="155" spans="1:6" ht="12.75">
-      <c r="A155" s="26" t="str">
+      <c r="A155" s="37" t="str">
         <f>CONCATENATE("Say ₹ ",F145," + ",F154," x Cost Index")</f>
-        <v>Say ₹ 120.22 + 29.66 x Cost Index</v>
+        <v>Say ₹ 80.14 + 29.66 x Cost Index</v>
       </c>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -3056,11 +3110,11 @@
       <c r="F155" s="3"/>
     </row>
     <row r="156" spans="1:6" ht="12.75">
-      <c r="A156" s="16" t="s">
+      <c r="A156" s="16">
+        <v>0</v>
+      </c>
+      <c r="B156" s="17" t="s">
         <v>41</v>
-      </c>
-      <c r="B156" s="17" t="s">
-        <v>42</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" s="2"/>
@@ -3109,10 +3163,10 @@
     </row>
     <row r="160" spans="1:6" ht="12.75">
       <c r="A160" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="B160" s="19" t="s">
         <v>43</v>
-      </c>
-      <c r="B160" s="19" t="s">
-        <v>44</v>
       </c>
       <c r="C160" s="20" t="s">
         <v>12</v>
@@ -3121,11 +3175,11 @@
         <v>11.50</v>
       </c>
       <c r="E160" s="20">
-        <v>118</v>
-      </c>
-      <c r="F160" s="27">
+        <v>90</v>
+      </c>
+      <c r="F160" s="21">
         <f>D160*E160</f>
-        <v>1357</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="161" spans="1:6" ht="12.75">
@@ -3148,7 +3202,7 @@
       <c r="E162" s="3"/>
       <c r="F162" s="23">
         <f>F160*0.01</f>
-        <v>13.57</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="163" spans="1:6" ht="12.75">
@@ -3161,7 +3215,7 @@
       <c r="E163" s="3"/>
       <c r="F163" s="23">
         <f>SUM(F160:F162)</f>
-        <v>1370.57</v>
+        <v>1045.35</v>
       </c>
     </row>
     <row r="164" spans="1:6" ht="12.75">
@@ -3174,7 +3228,7 @@
       <c r="E164" s="3"/>
       <c r="F164" s="23">
         <f>F163*0.15</f>
-        <v>205.5855</v>
+        <v>156.8025</v>
       </c>
     </row>
     <row r="165" spans="1:6" ht="12.75">
@@ -3187,7 +3241,7 @@
       <c r="E165" s="3"/>
       <c r="F165" s="23">
         <f>SUM(F163:F164)</f>
-        <v>1576.1555000000001</v>
+        <v>1202.1525</v>
       </c>
     </row>
     <row r="166" spans="1:6" ht="12.75">
@@ -3200,7 +3254,7 @@
       <c r="E166" s="3"/>
       <c r="F166" s="23">
         <f>F165</f>
-        <v>1576.1555000000001</v>
+        <v>1202.1525</v>
       </c>
     </row>
     <row r="167" spans="1:6" ht="12.75">
@@ -3213,7 +3267,7 @@
       <c r="E167" s="3"/>
       <c r="F167" s="24">
         <f>ROUND(F166/10,2)</f>
-        <v>157.62</v>
+        <v>120.22</v>
       </c>
     </row>
     <row r="168" spans="1:6" ht="12.75">
@@ -3350,9 +3404,9 @@
       </c>
     </row>
     <row r="177" spans="1:6" ht="12.75">
-      <c r="A177" s="26" t="str">
+      <c r="A177" s="37" t="str">
         <f>CONCATENATE("Say ₹ ",F167," + ",F176," x Cost Index")</f>
-        <v>Say ₹ 157.62 + 29.66 x Cost Index</v>
+        <v>Say ₹ 120.22 + 29.66 x Cost Index</v>
       </c>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -3361,11 +3415,11 @@
       <c r="F177" s="3"/>
     </row>
     <row r="178" spans="1:6" ht="12.75">
-      <c r="A178" s="4" t="s">
+      <c r="A178" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B178" s="28" t="s">
         <v>45</v>
-      </c>
-      <c r="B178" s="5" t="s">
-        <v>46</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
@@ -3373,38 +3427,38 @@
       <c r="F178" s="3"/>
     </row>
     <row r="179" spans="1:6" ht="12.75">
-      <c r="A179" s="4" t="s">
+      <c r="A179" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B179" s="4" t="s">
+      <c r="B179" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C179" s="4" t="s">
+      <c r="C179" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D179" s="4" t="s">
+      <c r="D179" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E179" s="4" t="s">
+      <c r="E179" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="F179" s="4" t="s">
+      <c r="F179" s="27" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="12.75">
-      <c r="A180" s="6"/>
-      <c r="B180" s="7" t="s">
+      <c r="A180" s="29"/>
+      <c r="B180" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C180" s="6"/>
-      <c r="D180" s="6"/>
-      <c r="E180" s="6"/>
-      <c r="F180" s="6"/>
+      <c r="C180" s="29"/>
+      <c r="D180" s="29"/>
+      <c r="E180" s="29"/>
+      <c r="F180" s="29"/>
     </row>
     <row r="181" spans="1:6" ht="12.75">
       <c r="A181" s="8"/>
-      <c r="B181" s="7" t="s">
+      <c r="B181" s="30" t="s">
         <v>9</v>
       </c>
       <c r="C181" s="8"/>
@@ -3413,29 +3467,29 @@
       <c r="F181" s="8"/>
     </row>
     <row r="182" spans="1:6" ht="12.75">
-      <c r="A182" s="9" t="s">
+      <c r="A182" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="B182" s="30" t="s">
         <v>47</v>
       </c>
-      <c r="B182" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C182" s="9" t="s">
+      <c r="C182" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="D182" s="9">
+      <c r="D182" s="31">
         <v>11.50</v>
       </c>
-      <c r="E182" s="9">
-        <v>129</v>
-      </c>
-      <c r="F182" s="10">
+      <c r="E182" s="31">
+        <v>118</v>
+      </c>
+      <c r="F182" s="38">
         <f>D182*E182</f>
-        <v>1483.50</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="12.75">
       <c r="A183" s="8"/>
-      <c r="B183" s="7" t="s">
+      <c r="B183" s="30" t="s">
         <v>13</v>
       </c>
       <c r="C183" s="8"/>
@@ -3444,220 +3498,220 @@
       <c r="F183" s="8"/>
     </row>
     <row r="184" spans="1:6" ht="12.75">
-      <c r="A184" s="7"/>
-      <c r="B184" s="11" t="s">
+      <c r="A184" s="30"/>
+      <c r="B184" s="33" t="s">
         <v>14</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" s="2"/>
       <c r="E184" s="3"/>
-      <c r="F184" s="12">
+      <c r="F184" s="34">
         <f>F182*0.01</f>
-        <v>14.835</v>
+        <v>13.57</v>
       </c>
     </row>
     <row r="185" spans="1:6" ht="12.75">
-      <c r="A185" s="7"/>
-      <c r="B185" s="11" t="s">
+      <c r="A185" s="30"/>
+      <c r="B185" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" s="2"/>
       <c r="E185" s="3"/>
-      <c r="F185" s="12">
+      <c r="F185" s="34">
         <f>SUM(F182:F184)</f>
-        <v>1498.335</v>
+        <v>1370.57</v>
       </c>
     </row>
     <row r="186" spans="1:6" ht="12.75">
-      <c r="A186" s="7"/>
-      <c r="B186" s="11" t="s">
+      <c r="A186" s="30"/>
+      <c r="B186" s="33" t="s">
         <v>16</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
       <c r="E186" s="3"/>
-      <c r="F186" s="12">
+      <c r="F186" s="34">
         <f>F185*0.15</f>
-        <v>224.75024999999999</v>
+        <v>205.5855</v>
       </c>
     </row>
     <row r="187" spans="1:6" ht="12.75">
-      <c r="A187" s="7"/>
-      <c r="B187" s="11" t="s">
+      <c r="A187" s="30"/>
+      <c r="B187" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" s="2"/>
       <c r="E187" s="3"/>
-      <c r="F187" s="12">
+      <c r="F187" s="34">
         <f>SUM(F185:F186)</f>
-        <v>1723.0852500000001</v>
+        <v>1576.1555000000001</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="12.75">
-      <c r="A188" s="7"/>
-      <c r="B188" s="11" t="s">
+      <c r="A188" s="30"/>
+      <c r="B188" s="33" t="s">
         <v>17</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" s="2"/>
       <c r="E188" s="3"/>
-      <c r="F188" s="12">
+      <c r="F188" s="34">
         <f>F187</f>
-        <v>1723.0852500000001</v>
+        <v>1576.1555000000001</v>
       </c>
     </row>
     <row r="189" spans="1:6" ht="12.75">
-      <c r="A189" s="7"/>
-      <c r="B189" s="11" t="s">
+      <c r="A189" s="30"/>
+      <c r="B189" s="33" t="s">
         <v>18</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
       <c r="E189" s="3"/>
-      <c r="F189" s="13">
+      <c r="F189" s="35">
         <f>ROUND(F188/10,2)</f>
-        <v>172.31</v>
+        <v>157.62</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="12.75">
-      <c r="A190" s="14">
+      <c r="A190" s="36">
         <v>116</v>
       </c>
-      <c r="B190" s="7" t="s">
+      <c r="B190" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C190" s="14" t="s">
+      <c r="C190" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="D190" s="14">
+      <c r="D190" s="36">
         <v>0.12</v>
       </c>
-      <c r="E190" s="14">
+      <c r="E190" s="36">
         <v>784</v>
       </c>
-      <c r="F190" s="12">
+      <c r="F190" s="34">
         <f>D190*E190</f>
         <v>94.08</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="12.75">
-      <c r="A191" s="14">
+      <c r="A191" s="36">
         <v>114</v>
       </c>
-      <c r="B191" s="7" t="s">
+      <c r="B191" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C191" s="14" t="s">
+      <c r="C191" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="D191" s="14">
+      <c r="D191" s="36">
         <v>0.25</v>
       </c>
-      <c r="E191" s="14">
+      <c r="E191" s="36">
         <v>645</v>
       </c>
-      <c r="F191" s="12">
+      <c r="F191" s="34">
         <f>D191*E191</f>
         <v>161.25</v>
       </c>
     </row>
     <row r="192" spans="1:6" ht="12.75">
-      <c r="A192" s="7"/>
-      <c r="B192" s="11" t="s">
+      <c r="A192" s="30"/>
+      <c r="B192" s="33" t="s">
         <v>22</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" s="2"/>
       <c r="E192" s="3"/>
-      <c r="F192" s="12">
+      <c r="F192" s="34">
         <f>SUM(F190:F191)</f>
         <v>255.33</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="12.75">
-      <c r="A193" s="7"/>
-      <c r="B193" s="11" t="s">
+      <c r="A193" s="30"/>
+      <c r="B193" s="33" t="s">
         <v>14</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" s="2"/>
       <c r="E193" s="3"/>
-      <c r="F193" s="12">
+      <c r="F193" s="34">
         <f>F192*0.01</f>
         <v>2.5533000000000001</v>
       </c>
     </row>
     <row r="194" spans="1:6" ht="12.75">
-      <c r="A194" s="7"/>
-      <c r="B194" s="11" t="s">
+      <c r="A194" s="30"/>
+      <c r="B194" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C194" s="2"/>
       <c r="D194" s="2"/>
       <c r="E194" s="3"/>
-      <c r="F194" s="12">
+      <c r="F194" s="34">
         <f>SUM(F192:F193)</f>
         <v>257.88330000000002</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="12.75">
-      <c r="A195" s="7"/>
-      <c r="B195" s="11" t="s">
+      <c r="A195" s="30"/>
+      <c r="B195" s="33" t="s">
         <v>16</v>
       </c>
       <c r="C195" s="2"/>
       <c r="D195" s="2"/>
       <c r="E195" s="3"/>
-      <c r="F195" s="12">
+      <c r="F195" s="34">
         <f>F194*0.15</f>
         <v>38.682495000000003</v>
       </c>
     </row>
     <row r="196" spans="1:6" ht="12.75">
-      <c r="A196" s="7"/>
-      <c r="B196" s="11" t="s">
+      <c r="A196" s="30"/>
+      <c r="B196" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" s="2"/>
       <c r="E196" s="3"/>
-      <c r="F196" s="12">
+      <c r="F196" s="34">
         <f>SUM(F194:F195)</f>
         <v>296.56579499999998</v>
       </c>
     </row>
     <row r="197" spans="1:6" ht="12.75">
-      <c r="A197" s="7"/>
-      <c r="B197" s="11" t="s">
+      <c r="A197" s="30"/>
+      <c r="B197" s="33" t="s">
         <v>17</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" s="2"/>
       <c r="E197" s="3"/>
-      <c r="F197" s="12">
+      <c r="F197" s="34">
         <f>F196</f>
         <v>296.56579499999998</v>
       </c>
     </row>
     <row r="198" spans="1:6" ht="12.75">
-      <c r="A198" s="7"/>
-      <c r="B198" s="11" t="s">
+      <c r="A198" s="30"/>
+      <c r="B198" s="33" t="s">
         <v>18</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
       <c r="E198" s="3"/>
-      <c r="F198" s="13">
+      <c r="F198" s="35">
         <f>ROUND(F197/10,2)</f>
         <v>29.66</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="12.75">
-      <c r="A199" s="26" t="str">
+      <c r="A199" s="37" t="str">
         <f>CONCATENATE("Say ₹ ",F189," + ",F198," x Cost Index")</f>
-        <v>Say ₹ 172.31 + 29.66 x Cost Index</v>
+        <v>Say ₹ 157.62 + 29.66 x Cost Index</v>
       </c>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -3667,10 +3721,10 @@
     </row>
     <row r="200" spans="1:6" ht="12.75">
       <c r="A200" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B200" s="17" t="s">
         <v>49</v>
-      </c>
-      <c r="B200" s="17" t="s">
-        <v>50</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
@@ -3719,10 +3773,10 @@
     </row>
     <row r="204" spans="1:6" ht="12.75">
       <c r="A204" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B204" s="19" t="s">
         <v>51</v>
-      </c>
-      <c r="B204" s="19" t="s">
-        <v>52</v>
       </c>
       <c r="C204" s="20" t="s">
         <v>12</v>
@@ -3731,11 +3785,11 @@
         <v>11.50</v>
       </c>
       <c r="E204" s="20">
-        <v>211</v>
-      </c>
-      <c r="F204" s="27">
+        <v>129</v>
+      </c>
+      <c r="F204" s="21">
         <f>D204*E204</f>
-        <v>2426.50</v>
+        <v>1483.50</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="12.75">
@@ -3758,7 +3812,7 @@
       <c r="E206" s="3"/>
       <c r="F206" s="23">
         <f>F204*0.01</f>
-        <v>24.265</v>
+        <v>14.835</v>
       </c>
     </row>
     <row r="207" spans="1:6" ht="12.75">
@@ -3771,7 +3825,7 @@
       <c r="E207" s="3"/>
       <c r="F207" s="23">
         <f>SUM(F204:F206)</f>
-        <v>2450.765</v>
+        <v>1498.335</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="12.75">
@@ -3784,7 +3838,7 @@
       <c r="E208" s="3"/>
       <c r="F208" s="23">
         <f>F207*0.15</f>
-        <v>367.61475000000002</v>
+        <v>224.75024999999999</v>
       </c>
     </row>
     <row r="209" spans="1:6" ht="12.75">
@@ -3797,7 +3851,7 @@
       <c r="E209" s="3"/>
       <c r="F209" s="23">
         <f>SUM(F207:F208)</f>
-        <v>2818.3797500000001</v>
+        <v>1723.0852500000001</v>
       </c>
     </row>
     <row r="210" spans="1:6" ht="12.75">
@@ -3810,7 +3864,7 @@
       <c r="E210" s="3"/>
       <c r="F210" s="23">
         <f>F209</f>
-        <v>2818.3797500000001</v>
+        <v>1723.0852500000001</v>
       </c>
     </row>
     <row r="211" spans="1:6" ht="12.75">
@@ -3823,7 +3877,7 @@
       <c r="E211" s="3"/>
       <c r="F211" s="24">
         <f>ROUND(F210/10,2)</f>
-        <v>281.84</v>
+        <v>172.31</v>
       </c>
     </row>
     <row r="212" spans="1:6" ht="12.75">
@@ -3960,9 +4014,9 @@
       </c>
     </row>
     <row r="221" spans="1:6" ht="12.75">
-      <c r="A221" s="26" t="str">
+      <c r="A221" s="37" t="str">
         <f>CONCATENATE("Say ₹ ",F211," + ",F220," x Cost Index")</f>
-        <v>Say ₹ 281.84 + 29.66 x Cost Index</v>
+        <v>Say ₹ 172.31 + 29.66 x Cost Index</v>
       </c>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -3971,11 +4025,11 @@
       <c r="F221" s="3"/>
     </row>
     <row r="222" spans="1:6" ht="12.75">
-      <c r="A222" s="4" t="s">
+      <c r="A222" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B222" s="28" t="s">
         <v>53</v>
-      </c>
-      <c r="B222" s="5" t="s">
-        <v>54</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" s="2"/>
@@ -3983,38 +4037,38 @@
       <c r="F222" s="3"/>
     </row>
     <row r="223" spans="1:6" ht="12.75">
-      <c r="A223" s="4" t="s">
+      <c r="A223" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B223" s="4" t="s">
+      <c r="B223" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C223" s="4" t="s">
+      <c r="C223" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D223" s="4" t="s">
+      <c r="D223" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E223" s="4" t="s">
+      <c r="E223" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="F223" s="4" t="s">
+      <c r="F223" s="27" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="224" spans="1:6" ht="12.75">
-      <c r="A224" s="6"/>
-      <c r="B224" s="7" t="s">
+      <c r="A224" s="29"/>
+      <c r="B224" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C224" s="6"/>
-      <c r="D224" s="6"/>
-      <c r="E224" s="6"/>
-      <c r="F224" s="6"/>
+      <c r="C224" s="29"/>
+      <c r="D224" s="29"/>
+      <c r="E224" s="29"/>
+      <c r="F224" s="29"/>
     </row>
     <row r="225" spans="1:6" ht="12.75">
       <c r="A225" s="8"/>
-      <c r="B225" s="7" t="s">
+      <c r="B225" s="30" t="s">
         <v>9</v>
       </c>
       <c r="C225" s="8"/>
@@ -4023,29 +4077,29 @@
       <c r="F225" s="8"/>
     </row>
     <row r="226" spans="1:6" ht="12.75">
-      <c r="A226" s="9" t="s">
+      <c r="A226" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B226" s="30" t="s">
         <v>55</v>
       </c>
-      <c r="B226" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C226" s="9" t="s">
+      <c r="C226" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="D226" s="9">
+      <c r="D226" s="31">
         <v>11.50</v>
       </c>
-      <c r="E226" s="9">
-        <v>520</v>
-      </c>
-      <c r="F226" s="10">
+      <c r="E226" s="31">
+        <v>211</v>
+      </c>
+      <c r="F226" s="38">
         <f>D226*E226</f>
-        <v>5980</v>
+        <v>2426.50</v>
       </c>
     </row>
     <row r="227" spans="1:6" ht="12.75">
       <c r="A227" s="8"/>
-      <c r="B227" s="7" t="s">
+      <c r="B227" s="30" t="s">
         <v>13</v>
       </c>
       <c r="C227" s="8"/>
@@ -4054,220 +4108,220 @@
       <c r="F227" s="8"/>
     </row>
     <row r="228" spans="1:6" ht="12.75">
-      <c r="A228" s="7"/>
-      <c r="B228" s="11" t="s">
+      <c r="A228" s="30"/>
+      <c r="B228" s="33" t="s">
         <v>14</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" s="2"/>
       <c r="E228" s="3"/>
-      <c r="F228" s="12">
+      <c r="F228" s="34">
         <f>F226*0.01</f>
-        <v>59.80</v>
+        <v>24.265</v>
       </c>
     </row>
     <row r="229" spans="1:6" ht="12.75">
-      <c r="A229" s="7"/>
-      <c r="B229" s="11" t="s">
+      <c r="A229" s="30"/>
+      <c r="B229" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" s="2"/>
       <c r="E229" s="3"/>
-      <c r="F229" s="12">
+      <c r="F229" s="34">
         <f>SUM(F226:F228)</f>
-        <v>6039.80</v>
+        <v>2450.765</v>
       </c>
     </row>
     <row r="230" spans="1:6" ht="12.75">
-      <c r="A230" s="7"/>
-      <c r="B230" s="11" t="s">
+      <c r="A230" s="30"/>
+      <c r="B230" s="33" t="s">
         <v>16</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" s="2"/>
       <c r="E230" s="3"/>
-      <c r="F230" s="12">
+      <c r="F230" s="34">
         <f>F229*0.15</f>
-        <v>905.97</v>
+        <v>367.61475000000002</v>
       </c>
     </row>
     <row r="231" spans="1:6" ht="12.75">
-      <c r="A231" s="7"/>
-      <c r="B231" s="11" t="s">
+      <c r="A231" s="30"/>
+      <c r="B231" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" s="2"/>
       <c r="E231" s="3"/>
-      <c r="F231" s="12">
+      <c r="F231" s="34">
         <f>SUM(F229:F230)</f>
-        <v>6945.77</v>
+        <v>2818.3797500000001</v>
       </c>
     </row>
     <row r="232" spans="1:6" ht="12.75">
-      <c r="A232" s="7"/>
-      <c r="B232" s="11" t="s">
+      <c r="A232" s="30"/>
+      <c r="B232" s="33" t="s">
         <v>17</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" s="2"/>
       <c r="E232" s="3"/>
-      <c r="F232" s="12">
+      <c r="F232" s="34">
         <f>F231</f>
-        <v>6945.77</v>
+        <v>2818.3797500000001</v>
       </c>
     </row>
     <row r="233" spans="1:6" ht="12.75">
-      <c r="A233" s="7"/>
-      <c r="B233" s="11" t="s">
+      <c r="A233" s="30"/>
+      <c r="B233" s="33" t="s">
         <v>18</v>
       </c>
       <c r="C233" s="2"/>
       <c r="D233" s="2"/>
       <c r="E233" s="3"/>
-      <c r="F233" s="13">
+      <c r="F233" s="35">
         <f>ROUND(F232/10,2)</f>
-        <v>694.58</v>
+        <v>281.84</v>
       </c>
     </row>
     <row r="234" spans="1:6" ht="12.75">
-      <c r="A234" s="14">
+      <c r="A234" s="36">
         <v>116</v>
       </c>
-      <c r="B234" s="7" t="s">
+      <c r="B234" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C234" s="14" t="s">
+      <c r="C234" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="D234" s="14">
+      <c r="D234" s="36">
         <v>0.12</v>
       </c>
-      <c r="E234" s="14">
+      <c r="E234" s="36">
         <v>784</v>
       </c>
-      <c r="F234" s="12">
+      <c r="F234" s="34">
         <f>D234*E234</f>
         <v>94.08</v>
       </c>
     </row>
     <row r="235" spans="1:6" ht="12.75">
-      <c r="A235" s="14">
+      <c r="A235" s="36">
         <v>114</v>
       </c>
-      <c r="B235" s="7" t="s">
+      <c r="B235" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C235" s="14" t="s">
+      <c r="C235" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="D235" s="14">
+      <c r="D235" s="36">
         <v>0.25</v>
       </c>
-      <c r="E235" s="14">
+      <c r="E235" s="36">
         <v>645</v>
       </c>
-      <c r="F235" s="12">
+      <c r="F235" s="34">
         <f>D235*E235</f>
         <v>161.25</v>
       </c>
     </row>
     <row r="236" spans="1:6" ht="12.75">
-      <c r="A236" s="7"/>
-      <c r="B236" s="11" t="s">
+      <c r="A236" s="30"/>
+      <c r="B236" s="33" t="s">
         <v>22</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" s="2"/>
       <c r="E236" s="3"/>
-      <c r="F236" s="12">
+      <c r="F236" s="34">
         <f>SUM(F234:F235)</f>
         <v>255.33</v>
       </c>
     </row>
     <row r="237" spans="1:6" ht="12.75">
-      <c r="A237" s="7"/>
-      <c r="B237" s="11" t="s">
+      <c r="A237" s="30"/>
+      <c r="B237" s="33" t="s">
         <v>14</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" s="2"/>
       <c r="E237" s="3"/>
-      <c r="F237" s="12">
+      <c r="F237" s="34">
         <f>F236*0.01</f>
         <v>2.5533000000000001</v>
       </c>
     </row>
     <row r="238" spans="1:6" ht="12.75">
-      <c r="A238" s="7"/>
-      <c r="B238" s="11" t="s">
+      <c r="A238" s="30"/>
+      <c r="B238" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" s="2"/>
       <c r="E238" s="3"/>
-      <c r="F238" s="12">
+      <c r="F238" s="34">
         <f>SUM(F236:F237)</f>
         <v>257.88330000000002</v>
       </c>
     </row>
     <row r="239" spans="1:6" ht="12.75">
-      <c r="A239" s="7"/>
-      <c r="B239" s="11" t="s">
+      <c r="A239" s="30"/>
+      <c r="B239" s="33" t="s">
         <v>16</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" s="2"/>
       <c r="E239" s="3"/>
-      <c r="F239" s="12">
+      <c r="F239" s="34">
         <f>F238*0.15</f>
         <v>38.682495000000003</v>
       </c>
     </row>
     <row r="240" spans="1:6" ht="12.75">
-      <c r="A240" s="7"/>
-      <c r="B240" s="11" t="s">
+      <c r="A240" s="30"/>
+      <c r="B240" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" s="2"/>
       <c r="E240" s="3"/>
-      <c r="F240" s="12">
+      <c r="F240" s="34">
         <f>SUM(F238:F239)</f>
         <v>296.56579499999998</v>
       </c>
     </row>
     <row r="241" spans="1:6" ht="12.75">
-      <c r="A241" s="7"/>
-      <c r="B241" s="11" t="s">
+      <c r="A241" s="30"/>
+      <c r="B241" s="33" t="s">
         <v>17</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" s="2"/>
       <c r="E241" s="3"/>
-      <c r="F241" s="12">
+      <c r="F241" s="34">
         <f>F240</f>
         <v>296.56579499999998</v>
       </c>
     </row>
     <row r="242" spans="1:6" ht="12.75">
-      <c r="A242" s="7"/>
-      <c r="B242" s="11" t="s">
+      <c r="A242" s="30"/>
+      <c r="B242" s="33" t="s">
         <v>18</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" s="2"/>
       <c r="E242" s="3"/>
-      <c r="F242" s="13">
+      <c r="F242" s="35">
         <f>ROUND(F241/10,2)</f>
         <v>29.66</v>
       </c>
     </row>
     <row r="243" spans="1:6" ht="12.75">
-      <c r="A243" s="26" t="str">
+      <c r="A243" s="37" t="str">
         <f>CONCATENATE("Say ₹ ",F233," + ",F242," x Cost Index")</f>
-        <v>Say ₹ 694.58 + 29.66 x Cost Index</v>
+        <v>Say ₹ 281.84 + 29.66 x Cost Index</v>
       </c>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -4276,8 +4330,8 @@
       <c r="F243" s="3"/>
     </row>
     <row r="244" spans="1:6" ht="12.75">
-      <c r="A244" s="16">
-        <v>0</v>
+      <c r="A244" s="16" t="s">
+        <v>56</v>
       </c>
       <c r="B244" s="17" t="s">
         <v>57</v>
@@ -4341,11 +4395,11 @@
         <v>11.50</v>
       </c>
       <c r="E248" s="20">
-        <v>475</v>
-      </c>
-      <c r="F248" s="27">
+        <v>520</v>
+      </c>
+      <c r="F248" s="21">
         <f>D248*E248</f>
-        <v>5462.50</v>
+        <v>5980</v>
       </c>
     </row>
     <row r="249" spans="1:6" ht="12.75">
@@ -4368,7 +4422,7 @@
       <c r="E250" s="3"/>
       <c r="F250" s="23">
         <f>F248*0.01</f>
-        <v>54.625</v>
+        <v>59.80</v>
       </c>
     </row>
     <row r="251" spans="1:6" ht="12.75">
@@ -4381,7 +4435,7 @@
       <c r="E251" s="3"/>
       <c r="F251" s="23">
         <f>SUM(F248:F250)</f>
-        <v>5517.125</v>
+        <v>6039.80</v>
       </c>
     </row>
     <row r="252" spans="1:6" ht="12.75">
@@ -4394,7 +4448,7 @@
       <c r="E252" s="3"/>
       <c r="F252" s="23">
         <f>F251*0.15</f>
-        <v>827.56875000000002</v>
+        <v>905.97</v>
       </c>
     </row>
     <row r="253" spans="1:6" ht="12.75">
@@ -4407,7 +4461,7 @@
       <c r="E253" s="3"/>
       <c r="F253" s="23">
         <f>SUM(F251:F252)</f>
-        <v>6344.6937500000004</v>
+        <v>6945.77</v>
       </c>
     </row>
     <row r="254" spans="1:6" ht="12.75">
@@ -4420,7 +4474,7 @@
       <c r="E254" s="3"/>
       <c r="F254" s="23">
         <f>F253</f>
-        <v>6344.6937500000004</v>
+        <v>6945.77</v>
       </c>
     </row>
     <row r="255" spans="1:6" ht="12.75">
@@ -4433,7 +4487,7 @@
       <c r="E255" s="3"/>
       <c r="F255" s="24">
         <f>ROUND(F254/10,2)</f>
-        <v>634.47</v>
+        <v>694.58</v>
       </c>
     </row>
     <row r="256" spans="1:6" ht="12.75">
@@ -4570,9 +4624,9 @@
       </c>
     </row>
     <row r="265" spans="1:6" ht="12.75">
-      <c r="A265" s="26" t="str">
+      <c r="A265" s="37" t="str">
         <f>CONCATENATE("Say ₹ ",F255," + ",F264," x Cost Index")</f>
-        <v>Say ₹ 634.47 + 29.66 x Cost Index</v>
+        <v>Say ₹ 694.58 + 29.66 x Cost Index</v>
       </c>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -4581,10 +4635,10 @@
       <c r="F265" s="3"/>
     </row>
     <row r="266" spans="1:6" ht="12.75">
-      <c r="A266" s="4">
+      <c r="A266" s="27">
         <v>0</v>
       </c>
-      <c r="B266" s="5" t="s">
+      <c r="B266" s="28" t="s">
         <v>60</v>
       </c>
       <c r="C266" s="2"/>
@@ -4593,38 +4647,38 @@
       <c r="F266" s="3"/>
     </row>
     <row r="267" spans="1:6" ht="12.75">
-      <c r="A267" s="4" t="s">
+      <c r="A267" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="B267" s="4" t="s">
+      <c r="B267" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C267" s="4" t="s">
+      <c r="C267" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="D267" s="4" t="s">
+      <c r="D267" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="E267" s="4" t="s">
+      <c r="E267" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="F267" s="4" t="s">
+      <c r="F267" s="27" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="268" spans="1:6" ht="12.75">
-      <c r="A268" s="6"/>
-      <c r="B268" s="7" t="s">
+      <c r="A268" s="29"/>
+      <c r="B268" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="C268" s="6"/>
-      <c r="D268" s="6"/>
-      <c r="E268" s="6"/>
-      <c r="F268" s="6"/>
+      <c r="C268" s="29"/>
+      <c r="D268" s="29"/>
+      <c r="E268" s="29"/>
+      <c r="F268" s="29"/>
     </row>
     <row r="269" spans="1:6" ht="12.75">
       <c r="A269" s="8"/>
-      <c r="B269" s="7" t="s">
+      <c r="B269" s="30" t="s">
         <v>9</v>
       </c>
       <c r="C269" s="8"/>
@@ -4633,29 +4687,29 @@
       <c r="F269" s="8"/>
     </row>
     <row r="270" spans="1:6" ht="12.75">
-      <c r="A270" s="9" t="s">
+      <c r="A270" s="31" t="s">
         <v>61</v>
       </c>
-      <c r="B270" s="7" t="s">
+      <c r="B270" s="30" t="s">
         <v>62</v>
       </c>
-      <c r="C270" s="9" t="s">
+      <c r="C270" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="D270" s="9">
+      <c r="D270" s="31">
         <v>11.50</v>
       </c>
-      <c r="E270" s="9">
-        <v>150</v>
-      </c>
-      <c r="F270" s="10">
+      <c r="E270" s="31">
+        <v>475</v>
+      </c>
+      <c r="F270" s="38">
         <f>D270*E270</f>
-        <v>1725</v>
+        <v>5462.50</v>
       </c>
     </row>
     <row r="271" spans="1:6" ht="12.75">
       <c r="A271" s="8"/>
-      <c r="B271" s="7" t="s">
+      <c r="B271" s="30" t="s">
         <v>13</v>
       </c>
       <c r="C271" s="8"/>
@@ -4664,218 +4718,523 @@
       <c r="F271" s="8"/>
     </row>
     <row r="272" spans="1:6" ht="12.75">
-      <c r="A272" s="7"/>
-      <c r="B272" s="11" t="s">
+      <c r="A272" s="30"/>
+      <c r="B272" s="33" t="s">
         <v>14</v>
       </c>
       <c r="C272" s="2"/>
       <c r="D272" s="2"/>
       <c r="E272" s="3"/>
-      <c r="F272" s="12">
+      <c r="F272" s="34">
         <f>F270*0.01</f>
-        <v>17.25</v>
+        <v>54.625</v>
       </c>
     </row>
     <row r="273" spans="1:6" ht="12.75">
-      <c r="A273" s="7"/>
-      <c r="B273" s="11" t="s">
+      <c r="A273" s="30"/>
+      <c r="B273" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
       <c r="E273" s="3"/>
-      <c r="F273" s="12">
+      <c r="F273" s="34">
         <f>SUM(F270:F272)</f>
-        <v>1742.25</v>
+        <v>5517.125</v>
       </c>
     </row>
     <row r="274" spans="1:6" ht="12.75">
-      <c r="A274" s="7"/>
-      <c r="B274" s="11" t="s">
+      <c r="A274" s="30"/>
+      <c r="B274" s="33" t="s">
         <v>16</v>
       </c>
       <c r="C274" s="2"/>
       <c r="D274" s="2"/>
       <c r="E274" s="3"/>
-      <c r="F274" s="12">
+      <c r="F274" s="34">
         <f>F273*0.15</f>
-        <v>261.3375</v>
+        <v>827.56875000000002</v>
       </c>
     </row>
     <row r="275" spans="1:6" ht="12.75">
-      <c r="A275" s="7"/>
-      <c r="B275" s="11" t="s">
+      <c r="A275" s="30"/>
+      <c r="B275" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C275" s="2"/>
       <c r="D275" s="2"/>
       <c r="E275" s="3"/>
-      <c r="F275" s="12">
+      <c r="F275" s="34">
         <f>SUM(F273:F274)</f>
-        <v>2003.5875000000001</v>
+        <v>6344.6937500000004</v>
       </c>
     </row>
     <row r="276" spans="1:6" ht="12.75">
-      <c r="A276" s="7"/>
-      <c r="B276" s="11" t="s">
+      <c r="A276" s="30"/>
+      <c r="B276" s="33" t="s">
         <v>17</v>
       </c>
       <c r="C276" s="2"/>
       <c r="D276" s="2"/>
       <c r="E276" s="3"/>
-      <c r="F276" s="12">
+      <c r="F276" s="34">
         <f>F275</f>
-        <v>2003.5875000000001</v>
+        <v>6344.6937500000004</v>
       </c>
     </row>
     <row r="277" spans="1:6" ht="12.75">
-      <c r="A277" s="7"/>
-      <c r="B277" s="11" t="s">
+      <c r="A277" s="30"/>
+      <c r="B277" s="33" t="s">
         <v>18</v>
       </c>
       <c r="C277" s="2"/>
       <c r="D277" s="2"/>
       <c r="E277" s="3"/>
-      <c r="F277" s="13">
+      <c r="F277" s="35">
         <f>ROUND(F276/10,2)</f>
-        <v>200.36</v>
+        <v>634.47</v>
       </c>
     </row>
     <row r="278" spans="1:6" ht="12.75">
-      <c r="A278" s="14">
+      <c r="A278" s="36">
         <v>116</v>
       </c>
-      <c r="B278" s="7" t="s">
+      <c r="B278" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="C278" s="14" t="s">
+      <c r="C278" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="D278" s="14">
+      <c r="D278" s="36">
         <v>0.12</v>
       </c>
-      <c r="E278" s="14">
+      <c r="E278" s="36">
         <v>784</v>
       </c>
-      <c r="F278" s="12">
+      <c r="F278" s="34">
         <f>D278*E278</f>
         <v>94.08</v>
       </c>
     </row>
     <row r="279" spans="1:6" ht="12.75">
-      <c r="A279" s="14">
+      <c r="A279" s="36">
         <v>114</v>
       </c>
-      <c r="B279" s="7" t="s">
+      <c r="B279" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="C279" s="14" t="s">
+      <c r="C279" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="D279" s="14">
+      <c r="D279" s="36">
         <v>0.25</v>
       </c>
-      <c r="E279" s="14">
+      <c r="E279" s="36">
         <v>645</v>
       </c>
-      <c r="F279" s="12">
+      <c r="F279" s="34">
         <f>D279*E279</f>
         <v>161.25</v>
       </c>
     </row>
     <row r="280" spans="1:6" ht="12.75">
-      <c r="A280" s="7"/>
-      <c r="B280" s="11" t="s">
+      <c r="A280" s="30"/>
+      <c r="B280" s="33" t="s">
         <v>22</v>
       </c>
       <c r="C280" s="2"/>
       <c r="D280" s="2"/>
       <c r="E280" s="3"/>
-      <c r="F280" s="12">
+      <c r="F280" s="34">
         <f>SUM(F278:F279)</f>
         <v>255.33</v>
       </c>
     </row>
     <row r="281" spans="1:6" ht="12.75">
-      <c r="A281" s="7"/>
-      <c r="B281" s="11" t="s">
+      <c r="A281" s="30"/>
+      <c r="B281" s="33" t="s">
         <v>14</v>
       </c>
       <c r="C281" s="2"/>
       <c r="D281" s="2"/>
       <c r="E281" s="3"/>
-      <c r="F281" s="12">
+      <c r="F281" s="34">
         <f>F280*0.01</f>
         <v>2.5533000000000001</v>
       </c>
     </row>
     <row r="282" spans="1:6" ht="12.75">
-      <c r="A282" s="7"/>
-      <c r="B282" s="11" t="s">
+      <c r="A282" s="30"/>
+      <c r="B282" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C282" s="2"/>
       <c r="D282" s="2"/>
       <c r="E282" s="3"/>
-      <c r="F282" s="12">
+      <c r="F282" s="34">
         <f>SUM(F280:F281)</f>
         <v>257.88330000000002</v>
       </c>
     </row>
     <row r="283" spans="1:6" ht="12.75">
-      <c r="A283" s="7"/>
-      <c r="B283" s="11" t="s">
+      <c r="A283" s="30"/>
+      <c r="B283" s="33" t="s">
         <v>16</v>
       </c>
       <c r="C283" s="2"/>
       <c r="D283" s="2"/>
       <c r="E283" s="3"/>
-      <c r="F283" s="12">
+      <c r="F283" s="34">
         <f>F282*0.15</f>
         <v>38.682495000000003</v>
       </c>
     </row>
     <row r="284" spans="1:6" ht="12.75">
-      <c r="A284" s="7"/>
-      <c r="B284" s="11" t="s">
+      <c r="A284" s="30"/>
+      <c r="B284" s="33" t="s">
         <v>15</v>
       </c>
       <c r="C284" s="2"/>
       <c r="D284" s="2"/>
       <c r="E284" s="3"/>
-      <c r="F284" s="12">
+      <c r="F284" s="34">
         <f>SUM(F282:F283)</f>
         <v>296.56579499999998</v>
       </c>
     </row>
     <row r="285" spans="1:6" ht="12.75">
-      <c r="A285" s="7"/>
-      <c r="B285" s="11" t="s">
+      <c r="A285" s="30"/>
+      <c r="B285" s="33" t="s">
         <v>17</v>
       </c>
       <c r="C285" s="2"/>
       <c r="D285" s="2"/>
       <c r="E285" s="3"/>
-      <c r="F285" s="12">
+      <c r="F285" s="34">
         <f>F284</f>
         <v>296.56579499999998</v>
       </c>
     </row>
     <row r="286" spans="1:6" ht="12.75">
-      <c r="A286" s="7"/>
-      <c r="B286" s="11" t="s">
+      <c r="A286" s="30"/>
+      <c r="B286" s="33" t="s">
         <v>18</v>
       </c>
       <c r="C286" s="2"/>
       <c r="D286" s="2"/>
       <c r="E286" s="3"/>
-      <c r="F286" s="13">
+      <c r="F286" s="35">
         <f>ROUND(F285/10,2)</f>
         <v>29.66</v>
       </c>
     </row>
+    <row r="287" spans="1:6" ht="12.75">
+      <c r="A287" s="37" t="str">
+        <f>CONCATENATE("Say ₹ ",F277," + ",F286," x Cost Index")</f>
+        <v>Say ₹ 634.47 + 29.66 x Cost Index</v>
+      </c>
+      <c r="B287" s="2"/>
+      <c r="C287" s="2"/>
+      <c r="D287" s="2"/>
+      <c r="E287" s="2"/>
+      <c r="F287" s="3"/>
+    </row>
+    <row r="288" spans="1:6" ht="12.75">
+      <c r="A288" s="16">
+        <v>0</v>
+      </c>
+      <c r="B288" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="C288" s="2"/>
+      <c r="D288" s="2"/>
+      <c r="E288" s="2"/>
+      <c r="F288" s="3"/>
+    </row>
+    <row r="289" spans="1:6" ht="12.75">
+      <c r="A289" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="B289" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C289" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="D289" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="E289" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="F289" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" ht="12.75">
+      <c r="A290" s="18"/>
+      <c r="B290" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="C290" s="18"/>
+      <c r="D290" s="18"/>
+      <c r="E290" s="18"/>
+      <c r="F290" s="18"/>
+    </row>
+    <row r="291" spans="1:6" ht="12.75">
+      <c r="A291" s="8"/>
+      <c r="B291" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="C291" s="8"/>
+      <c r="D291" s="8"/>
+      <c r="E291" s="8"/>
+      <c r="F291" s="8"/>
+    </row>
+    <row r="292" spans="1:6" ht="12.75">
+      <c r="A292" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B292" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="C292" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D292" s="20">
+        <v>11.50</v>
+      </c>
+      <c r="E292" s="20">
+        <v>150</v>
+      </c>
+      <c r="F292" s="21">
+        <f>D292*E292</f>
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" ht="12.75">
+      <c r="A293" s="8"/>
+      <c r="B293" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="C293" s="8"/>
+      <c r="D293" s="8"/>
+      <c r="E293" s="8"/>
+      <c r="F293" s="8"/>
+    </row>
+    <row r="294" spans="1:6" ht="12.75">
+      <c r="A294" s="19"/>
+      <c r="B294" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C294" s="2"/>
+      <c r="D294" s="2"/>
+      <c r="E294" s="3"/>
+      <c r="F294" s="23">
+        <f>F292*0.01</f>
+        <v>17.25</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" ht="12.75">
+      <c r="A295" s="19"/>
+      <c r="B295" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C295" s="2"/>
+      <c r="D295" s="2"/>
+      <c r="E295" s="3"/>
+      <c r="F295" s="23">
+        <f>SUM(F292:F294)</f>
+        <v>1742.25</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" ht="12.75">
+      <c r="A296" s="19"/>
+      <c r="B296" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C296" s="2"/>
+      <c r="D296" s="2"/>
+      <c r="E296" s="3"/>
+      <c r="F296" s="23">
+        <f>F295*0.15</f>
+        <v>261.3375</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" ht="12.75">
+      <c r="A297" s="19"/>
+      <c r="B297" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C297" s="2"/>
+      <c r="D297" s="2"/>
+      <c r="E297" s="3"/>
+      <c r="F297" s="23">
+        <f>SUM(F295:F296)</f>
+        <v>2003.5875000000001</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" ht="12.75">
+      <c r="A298" s="19"/>
+      <c r="B298" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C298" s="2"/>
+      <c r="D298" s="2"/>
+      <c r="E298" s="3"/>
+      <c r="F298" s="23">
+        <f>F297</f>
+        <v>2003.5875000000001</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" ht="12.75">
+      <c r="A299" s="19"/>
+      <c r="B299" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C299" s="2"/>
+      <c r="D299" s="2"/>
+      <c r="E299" s="3"/>
+      <c r="F299" s="24">
+        <f>ROUND(F298/10,2)</f>
+        <v>200.36</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" ht="12.75">
+      <c r="A300" s="25">
+        <v>116</v>
+      </c>
+      <c r="B300" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C300" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D300" s="25">
+        <v>0.12</v>
+      </c>
+      <c r="E300" s="25">
+        <v>784</v>
+      </c>
+      <c r="F300" s="23">
+        <f>D300*E300</f>
+        <v>94.08</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" ht="12.75">
+      <c r="A301" s="25">
+        <v>114</v>
+      </c>
+      <c r="B301" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="C301" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D301" s="25">
+        <v>0.25</v>
+      </c>
+      <c r="E301" s="25">
+        <v>645</v>
+      </c>
+      <c r="F301" s="23">
+        <f>D301*E301</f>
+        <v>161.25</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" ht="12.75">
+      <c r="A302" s="19"/>
+      <c r="B302" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C302" s="2"/>
+      <c r="D302" s="2"/>
+      <c r="E302" s="3"/>
+      <c r="F302" s="23">
+        <f>SUM(F300:F301)</f>
+        <v>255.33</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" ht="12.75">
+      <c r="A303" s="19"/>
+      <c r="B303" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="C303" s="2"/>
+      <c r="D303" s="2"/>
+      <c r="E303" s="3"/>
+      <c r="F303" s="23">
+        <f>F302*0.01</f>
+        <v>2.5533000000000001</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" ht="12.75">
+      <c r="A304" s="19"/>
+      <c r="B304" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C304" s="2"/>
+      <c r="D304" s="2"/>
+      <c r="E304" s="3"/>
+      <c r="F304" s="23">
+        <f>SUM(F302:F303)</f>
+        <v>257.88330000000002</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" ht="12.75">
+      <c r="A305" s="19"/>
+      <c r="B305" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C305" s="2"/>
+      <c r="D305" s="2"/>
+      <c r="E305" s="3"/>
+      <c r="F305" s="23">
+        <f>F304*0.15</f>
+        <v>38.682495000000003</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" ht="12.75">
+      <c r="A306" s="19"/>
+      <c r="B306" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="C306" s="2"/>
+      <c r="D306" s="2"/>
+      <c r="E306" s="3"/>
+      <c r="F306" s="23">
+        <f>SUM(F304:F305)</f>
+        <v>296.56579499999998</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" ht="12.75">
+      <c r="A307" s="19"/>
+      <c r="B307" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C307" s="2"/>
+      <c r="D307" s="2"/>
+      <c r="E307" s="3"/>
+      <c r="F307" s="23">
+        <f>F306</f>
+        <v>296.56579499999998</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" ht="12.75">
+      <c r="A308" s="19"/>
+      <c r="B308" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C308" s="2"/>
+      <c r="D308" s="2"/>
+      <c r="E308" s="3"/>
+      <c r="F308" s="24">
+        <f>ROUND(F307/10,2)</f>
+        <v>29.66</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="325">
+  <mergeCells count="350">
     <mergeCell ref="B128:E128"/>
     <mergeCell ref="B129:E129"/>
     <mergeCell ref="B130:E130"/>
@@ -4977,36 +5336,6 @@
     <mergeCell ref="E248:E249"/>
     <mergeCell ref="F248:F249"/>
     <mergeCell ref="B250:E250"/>
-    <mergeCell ref="B260:E260"/>
-    <mergeCell ref="B261:E261"/>
-    <mergeCell ref="B262:E262"/>
-    <mergeCell ref="B263:E263"/>
-    <mergeCell ref="B264:E264"/>
-    <mergeCell ref="A265:F265"/>
-    <mergeCell ref="B266:F266"/>
-    <mergeCell ref="D270:D271"/>
-    <mergeCell ref="E270:E271"/>
-    <mergeCell ref="A268:A269"/>
-    <mergeCell ref="C268:C269"/>
-    <mergeCell ref="D268:D269"/>
-    <mergeCell ref="E268:E269"/>
-    <mergeCell ref="F268:F269"/>
-    <mergeCell ref="A270:A271"/>
-    <mergeCell ref="F270:F271"/>
-    <mergeCell ref="B280:E280"/>
-    <mergeCell ref="B281:E281"/>
-    <mergeCell ref="B282:E282"/>
-    <mergeCell ref="B283:E283"/>
-    <mergeCell ref="B284:E284"/>
-    <mergeCell ref="B285:E285"/>
-    <mergeCell ref="B286:E286"/>
-    <mergeCell ref="C270:C271"/>
-    <mergeCell ref="B272:E272"/>
-    <mergeCell ref="B273:E273"/>
-    <mergeCell ref="B274:E274"/>
-    <mergeCell ref="B275:E275"/>
-    <mergeCell ref="B276:E276"/>
-    <mergeCell ref="B277:E277"/>
     <mergeCell ref="B192:E192"/>
     <mergeCell ref="B193:E193"/>
     <mergeCell ref="B194:E194"/>
@@ -5046,6 +5375,61 @@
     <mergeCell ref="B255:E255"/>
     <mergeCell ref="B258:E258"/>
     <mergeCell ref="B259:E259"/>
+    <mergeCell ref="A287:F287"/>
+    <mergeCell ref="B288:F288"/>
+    <mergeCell ref="A290:A291"/>
+    <mergeCell ref="D290:D291"/>
+    <mergeCell ref="E290:E291"/>
+    <mergeCell ref="F290:F291"/>
+    <mergeCell ref="A292:A293"/>
+    <mergeCell ref="B302:E302"/>
+    <mergeCell ref="B303:E303"/>
+    <mergeCell ref="B304:E304"/>
+    <mergeCell ref="B305:E305"/>
+    <mergeCell ref="B306:E306"/>
+    <mergeCell ref="B307:E307"/>
+    <mergeCell ref="B308:E308"/>
+    <mergeCell ref="F292:F293"/>
+    <mergeCell ref="B294:E294"/>
+    <mergeCell ref="B295:E295"/>
+    <mergeCell ref="B296:E296"/>
+    <mergeCell ref="B297:E297"/>
+    <mergeCell ref="B298:E298"/>
+    <mergeCell ref="B299:E299"/>
+    <mergeCell ref="B260:E260"/>
+    <mergeCell ref="B261:E261"/>
+    <mergeCell ref="B262:E262"/>
+    <mergeCell ref="B263:E263"/>
+    <mergeCell ref="B264:E264"/>
+    <mergeCell ref="A265:F265"/>
+    <mergeCell ref="B266:F266"/>
+    <mergeCell ref="D270:D271"/>
+    <mergeCell ref="E270:E271"/>
+    <mergeCell ref="A268:A269"/>
+    <mergeCell ref="C268:C269"/>
+    <mergeCell ref="D268:D269"/>
+    <mergeCell ref="E268:E269"/>
+    <mergeCell ref="F268:F269"/>
+    <mergeCell ref="A270:A271"/>
+    <mergeCell ref="F270:F271"/>
+    <mergeCell ref="C270:C271"/>
+    <mergeCell ref="B272:E272"/>
+    <mergeCell ref="B273:E273"/>
+    <mergeCell ref="B274:E274"/>
+    <mergeCell ref="B275:E275"/>
+    <mergeCell ref="B276:E276"/>
+    <mergeCell ref="B277:E277"/>
+    <mergeCell ref="B280:E280"/>
+    <mergeCell ref="B281:E281"/>
+    <mergeCell ref="B282:E282"/>
+    <mergeCell ref="B283:E283"/>
+    <mergeCell ref="B284:E284"/>
+    <mergeCell ref="B285:E285"/>
+    <mergeCell ref="B286:E286"/>
+    <mergeCell ref="C290:C291"/>
+    <mergeCell ref="C292:C293"/>
+    <mergeCell ref="D292:D293"/>
+    <mergeCell ref="E292:E293"/>
     <mergeCell ref="C4:C5"/>
     <mergeCell ref="C6:C7"/>
     <mergeCell ref="D6:D7"/>

--- a/Side Bar Files/GWD Data/PVC wo Trench.xlsx
+++ b/Side Bar Files/GWD Data/PVC wo Trench.xlsx
@@ -831,7 +831,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B584226-AD90-43CD-850E-63175F09BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD5FB1CE-742C-4A03-A116-A73BA969BAA6}">
   <dimension ref="A1:F88"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>

--- a/Side Bar Files/GWD Data/PVC wo Trench.xlsx
+++ b/Side Bar Files/GWD Data/PVC wo Trench.xlsx
@@ -13,8 +13,8 @@
     <externalReference r:id="rId5"/>
   </externalReferences>
   <definedNames>
-    <definedName name="LMRRates">[1]LMR!$C:$C</definedName>
-    <definedName name="LMRCodes">[1]LMR!$A:$A</definedName>
+    <definedName name="LMRRates">[1]zLMR!$C:$C</definedName>
+    <definedName name="LMRCodes">[1]zLMR!$A:$A</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -476,10 +476,10 @@
       <sheetName val="Water Tank"/>
       <sheetName val="Well Protection"/>
       <sheetName val="WTP"/>
-      <sheetName val="Derived"/>
-      <sheetName val="LMR"/>
-      <sheetName val="PAMR39"/>
-      <sheetName val="ZCost Index"/>
+      <sheetName val="zCost Index"/>
+      <sheetName val="zDerived"/>
+      <sheetName val="zLMR"/>
+      <sheetName val="zPAMR39"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -831,7 +831,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD5FB1CE-742C-4A03-A116-A73BA969BAA6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E40A763-A636-474B-88B4-F787A91CBAA6}">
   <dimension ref="A1:F88"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <sheetData>
